--- a/output/pdf_financials_xlsx/TTI.xlsx
+++ b/output/pdf_financials_xlsx/TTI.xlsx
@@ -918,19 +918,19 @@
         <v>-0.128162</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.218262</v>
+        <v>-1.218262</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3.924251</v>
+        <v>-3.924251</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>5.063011</v>
+        <v>-5.063011</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3.14573</v>
+        <v>-3.14573</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>7.426077</v>
+        <v>-7.426077</v>
       </c>
     </row>
     <row r="17">
@@ -1078,19 +1078,19 @@
         <v>-0.128162</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.218262</v>
+        <v>-1.218262</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3.924251</v>
+        <v>-3.924251</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>5.063011</v>
+        <v>-5.063011</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.14573</v>
+        <v>-3.14573</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.426077</v>
+        <v>-7.426077</v>
       </c>
     </row>
     <row r="21">
@@ -1175,19 +1175,19 @@
         <v>-0.128162</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.218262</v>
+        <v>-1.218262</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.924251</v>
+        <v>-3.924251</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>5.063011</v>
+        <v>-5.063011</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.14573</v>
+        <v>-3.14573</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>7.426077</v>
+        <v>-7.426077</v>
       </c>
     </row>
     <row r="24">
@@ -1276,19 +1276,19 @@
         <v>1.28162</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-11.075109</v>
+        <v>11.075109</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-24.526569</v>
+        <v>24.526569</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-38.946238</v>
+        <v>38.946238</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-44.939</v>
+        <v>44.939</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-49.50718</v>
+        <v>49.50718</v>
       </c>
     </row>
     <row r="27">
@@ -1309,19 +1309,19 @@
         <v>-0.128162</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.218262</v>
+        <v>-1.218262</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.924251</v>
+        <v>-3.924251</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>5.063011</v>
+        <v>-5.063011</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3.14573</v>
+        <v>-3.14573</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>7.426077</v>
+        <v>-7.426077</v>
       </c>
     </row>
     <row r="28">
@@ -1375,19 +1375,19 @@
         <v>-0.128162</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.218262</v>
+        <v>-1.218262</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.924251</v>
+        <v>-3.924251</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>5.063011</v>
+        <v>-5.063011</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.14573</v>
+        <v>-3.14573</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>7.426077</v>
+        <v>-7.426077</v>
       </c>
     </row>
     <row r="30">
@@ -1455,19 +1455,19 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3500,19 +3500,19 @@
         <v>0.042447</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.042389</v>
+        <v>0.029975</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.08988400000000001</v>
+        <v>1.055011</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.672463</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.618548</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.420399</v>
       </c>
     </row>
     <row r="93">
@@ -5564,7 +5564,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -6046,7 +6050,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -6918,7 +6926,11 @@
           <t>Reserves (Note 10) 1,055,011 37,174</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -13205,19 +13217,19 @@
         </is>
       </c>
       <c r="H149" s="5" t="n">
-        <v>1.218262</v>
+        <v>-1.218262</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>3.924251</v>
+        <v>-3.924251</v>
       </c>
       <c r="J149" s="5" t="n">
-        <v>5.063011</v>
+        <v>-5.063011</v>
       </c>
       <c r="K149" s="5" t="n">
-        <v>3.14573</v>
+        <v>-3.14573</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>7.426077</v>
+        <v>-7.426077</v>
       </c>
     </row>
     <row r="150">

--- a/output/pdf_financials_xlsx/TTI.xlsx
+++ b/output/pdf_financials_xlsx/TTI.xlsx
@@ -789,16 +789,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006181</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.171165</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.200327</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.048722</v>
       </c>
     </row>
     <row r="13">
@@ -1312,16 +1312,16 @@
         <v>-1.218262</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.924251</v>
+        <v>-3.91807</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.063011</v>
+        <v>-4.891846</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.14573</v>
+        <v>-2.945403</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-7.426077</v>
+        <v>-7.377355</v>
       </c>
     </row>
     <row r="28">
@@ -1378,16 +1378,16 @@
         <v>-1.218262</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.924251</v>
+        <v>-3.91807</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.063011</v>
+        <v>-4.891846</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.14573</v>
+        <v>-2.945403</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-7.426077</v>
+        <v>-7.377355</v>
       </c>
     </row>
     <row r="30">
@@ -1539,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.182199</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.019188</v>
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.182199</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.019188</v>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
